--- a/Configs/GameConfig/Datas/cell/#Ability-主动技能.xlsx
+++ b/Configs/GameConfig/Datas/cell/#Ability-主动技能.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1791,6 +1791,49 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>29</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>召唤共生体</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>同时召唤孢子仆从、噬菌体与菌丝体三种附属体（共享附属体上限）。</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>25</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>spore,summon</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
